--- a/java-examples/replica-read-routing/docs/benchmark-results.xlsx
+++ b/java-examples/replica-read-routing/docs/benchmark-results.xlsx
@@ -866,7 +866,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FalkorDB Cloud, AWS us-east-2, 1 primary + 1 replica, THREAD_COUNT=2 per node, 1,980,000 nodes, 90 seconds per row.</t>
+          <t>FalkorDB Cloud, AWS us-east-2, 1 primary + 1 replica, 2 cores per DB pod, THREAD_COUNT=2 per node, 4 core client (EC2 c4.xlarge), 1,980,000 nodes, 90 seconds per row.</t>
         </is>
       </c>
     </row>
